--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1959,6 +1959,200 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128412198</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Harghults kalkbarrskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>529695</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6361261</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ökna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128413119</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97559</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Harghults kalkbarrskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>529734</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6361213</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ökna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Janne Kolehmainen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97353</v>
+        <v>97355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97559</v>
+        <v>97561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97561</v>
+        <v>97654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97654</v>
+        <v>97666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97666</v>
+        <v>97668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97669</v>
+        <v>97696</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97696</v>
+        <v>97709</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 2491-2021 artfynd.xlsx
+++ b/artfynd/A 2491-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128412198</v>
       </c>
       <c r="B12" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>128413119</v>
       </c>
       <c r="B13" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
